--- a/data/trans_bre/P19C08-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19C08-Estudios-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,8</t>
+          <t>-0,6; 0,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,31</t>
+          <t>-1,41; 0,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,5</t>
+          <t>-1,45; 0,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,61</t>
+          <t>0,07; 0,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-77,51; —</t>
+          <t>-86,23; 695,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,9</t>
+          <t>0,07; 0,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,85</t>
+          <t>-0,37; 0,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,33</t>
+          <t>0,0; 0,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,09</t>
+          <t>-0,96; 0,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,51; 265,28</t>
+          <t>-50,04; 313,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-84,11; 30,5</t>
+          <t>-83,64; 42,48</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,03</t>
+          <t>-1,65; 0,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,78</t>
+          <t>-1,32; 0,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,42</t>
+          <t>-0,41; 1,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,53</t>
+          <t>-0,17; 1,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 280,24</t>
+          <t>-100,0; 281,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-68,9; —</t>
+          <t>-73,66; 1326,18</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,58</t>
+          <t>-0,16; 0,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,4</t>
+          <t>-0,43; 0,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,32</t>
+          <t>-0,17; 0,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,21</t>
+          <t>-0,47; 0,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,53; 294,33</t>
+          <t>-37,19; 318,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,97; 109,46</t>
+          <t>-50,17; 106,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-79,05; 539,44</t>
+          <t>-73,69; 565,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,99; 83,3</t>
+          <t>-68,55; 82,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C08-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19C08-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,75</t>
+          <t>-0,57; 0,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,24</t>
+          <t>-1,34; 0,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,37</t>
+          <t>-1,45; 0,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,65</t>
+          <t>0,08; 0,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-86,23; 695,83</t>
+          <t>-81,19; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 224,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,37</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-48,95%</t>
+          <t>-50,21%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,96</t>
+          <t>0,07; 0,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,88</t>
+          <t>-0,32; 0,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,28</t>
+          <t>0,0; 0,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,11</t>
+          <t>-0,97; 0,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,04; 313,78</t>
+          <t>-45,72; 336,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-83,64; 42,48</t>
+          <t>-80,98; 30,91</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>159,11%</t>
+          <t>160,22%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,94</t>
+          <t>-1,4; 1,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,66</t>
+          <t>-1,3; 0,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,38</t>
+          <t>-0,41; 1,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,47</t>
+          <t>-0,14; 1,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 281,76</t>
+          <t>-100,0; 425,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-73,66; 1326,18</t>
+          <t>-67,83; 1207,18</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-15,4%</t>
+          <t>-16,43%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,57</t>
+          <t>-0,13; 0,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,4</t>
+          <t>-0,44; 0,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 0,31</t>
+          <t>-0,17; 0,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,22</t>
+          <t>-0,44; 0,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,19; 318,01</t>
+          <t>-35,19; 304,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,17; 106,94</t>
+          <t>-51,7; 89,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-73,69; 565,75</t>
+          <t>-75,72; 563,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,55; 82,74</t>
+          <t>-58,03; 100,03</t>
         </is>
       </c>
     </row>
